--- a/samples/sample_1_excess_intake.xlsx
+++ b/samples/sample_1_excess_intake.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>452661932490</t>
+          <t>873923542950</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14/06/2004</t>
+          <t>13/06/2005</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 75057 69614</t>
+          <t>+91 96583 76369</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>07194975212</t>
+          <t>07899355976</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>28-09-2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>203671869026</t>
+          <t>312914950317</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>08.01.2007</t>
+          <t>13/08/2007</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 78794 95899</t>
+          <t>+91 94871 12620</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08711801006</t>
+          <t>08145757506</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>01.09.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>686674257897</t>
+          <t>780264275923</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,17 +687,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2004-10-09</t>
+          <t>27/02/2006</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 80688 43446</t>
+          <t>+91 81089 40725</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09502069455</t>
+          <t>09969113350</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,24 +742,24 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>09.08.2026</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>123828472556</t>
+          <t>637031822213</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25/05/2007</t>
+          <t>2008-02-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 97975 49780</t>
+          <t>+91 93885 86594</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>07270248074</t>
+          <t>08911848521</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -829,19 +829,19 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>30-09-2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>312495548925</t>
+          <t>684534811895</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27-06-2007</t>
+          <t>25-03-2005</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 75190 44244</t>
+          <t>+91 86502 91787</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>08888693853</t>
+          <t>07848892378</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>16-08-2026</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>842813883772</t>
+          <t>700012492256</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2007-08-21</t>
+          <t>03-11-2008</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 81116 78785</t>
+          <t>+91 79689 54988</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>09422539408</t>
+          <t>07943996495</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>12.09.2026</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>227662247601</t>
+          <t>559095358077</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>20-02-2006</t>
+          <t>27.05.2007</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 72662 43552</t>
+          <t>+91 91730 13359</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>08546264509</t>
+          <t>07866759867</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1075,19 +1075,19 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>30/08/2026</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>771633537656</t>
+          <t>579185746457</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1097,27 +1097,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>24-03-2008</t>
+          <t>2007-06-27</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 81262 88640</t>
+          <t>+91 84616 63366</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>09430461176</t>
+          <t>08795131191</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1152,24 +1152,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>596014236271</t>
+          <t>937976137248</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11/01/2005</t>
+          <t>2004-01-03</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 92577 77585</t>
+          <t>+91 93205 29468</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>08110517152</t>
+          <t>09596064016</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>286403367577</t>
+          <t>916562398890</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2007-10-05</t>
+          <t>22-07-2006</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 89815 50903</t>
+          <t>+91 70096 94652</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>08531509480</t>
+          <t>09143272812</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1321,19 +1321,19 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>13/08/2026</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>198428144388</t>
+          <t>190713794933</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1343,27 +1343,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2004-12-04</t>
+          <t>2005-06-14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 79093 46344</t>
+          <t>+91 95893 30253</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>07821293682</t>
+          <t>08636759492</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>809209498752</t>
+          <t>720499500655</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2004-05-22</t>
+          <t>24-09-2007</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 73184 54510</t>
+          <t>+91 71668 35887</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>07414900223</t>
+          <t>07210138901</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>245075794394</t>
+          <t>125368456450</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17/06/2005</t>
+          <t>20.12.2004</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 73162 19007</t>
+          <t>+91 94542 88669</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09019418047</t>
+          <t>09158575829</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1585,19 +1585,19 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>874636722004</t>
+          <t>317528375691</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>15-08-2006</t>
+          <t>24-07-2008</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 75858 73542</t>
+          <t>+91 99781 20469</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>08258042768</t>
+          <t>08378813437</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1667,19 +1667,19 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>11/07/2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>919975714918</t>
+          <t>668313629943</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>21/07/2005</t>
+          <t>24-07-2008</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 71111 75783</t>
+          <t>+91 97712 24325</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07048904334</t>
+          <t>07840701489</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>18.07.2026</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>464489369321</t>
+          <t>855566208562</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>06/10/2004</t>
+          <t>13-05-2005</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 85891 15648</t>
+          <t>+91 76418 74217</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08162588096</t>
+          <t>09271753193</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>23.06.2026</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>628355491356</t>
+          <t>563808144683</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20-04-2004</t>
+          <t>28-12-2007</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 73416 71925</t>
+          <t>+91 96352 76091</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>09395862318</t>
+          <t>08153654077</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1908,24 +1908,24 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>05.07.2026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>124595579071</t>
+          <t>922506488115</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1935,27 +1935,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2004-01-20</t>
+          <t>2006-04-08</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 80881 78457</t>
+          <t>+91 87211 35609</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>07251193581</t>
+          <t>08580292163</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1990,24 +1990,24 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>24.06.2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>641951804619</t>
+          <t>963482292665</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2017,27 +2017,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>09/02/2007</t>
+          <t>06/11/2004</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 84213 71491</t>
+          <t>+91 92447 44686</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>09225749878</t>
+          <t>07373854687</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>30-08-2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>409584723777</t>
+          <t>821471690399</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2008-04-08</t>
+          <t>05-02-2008</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 86791 99279</t>
+          <t>+91 98149 27997</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09289048830</t>
+          <t>09807371788</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>04-07-2026</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>909066576754</t>
+          <t>494037713474</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2186,22 +2186,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>08/06/2008</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 92696 59206</t>
+          <t>+91 93638 89892</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>09542619072</t>
+          <t>08494848912</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>328897862405</t>
+          <t>172079013329</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,27 +2263,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2008-04-17</t>
+          <t>2007-03-14</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 75158 82607</t>
+          <t>+91 75789 54165</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>07130695457</t>
+          <t>07854388522</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>02/09/2026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>491754713250</t>
+          <t>908494315009</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2345,17 +2345,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>11/03/2008</t>
+          <t>21/09/2005</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 83276 80225</t>
+          <t>+91 72718 28021</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>08158260504</t>
+          <t>07569745084</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>343241508351</t>
+          <t>166316080098</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>20-04-2007</t>
+          <t>05-03-2005</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 70682 81901</t>
+          <t>+91 88951 99987</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>09642274202</t>
+          <t>08597911366</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2487,19 +2487,19 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>181124958167</t>
+          <t>404246197950</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2509,27 +2509,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>03-06-2007</t>
+          <t>16-11-2006</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 87353 30446</t>
+          <t>+91 87252 61204</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08794882773</t>
+          <t>07578904703</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2564,24 +2564,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>23/07/2026</t>
+          <t>15.09.2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>377769030136</t>
+          <t>511753973988</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>12.12.2007</t>
+          <t>02-07-2006</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 87742 91299</t>
+          <t>+91 70905 91452</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>09301915580</t>
+          <t>07615153189</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2646,24 +2646,24 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>937131336241</t>
+          <t>720302914508</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2673,27 +2673,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2008-12-11</t>
+          <t>25-03-2008</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 84096 36967</t>
+          <t>+91 89701 95973</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>08851784025</t>
+          <t>08583639297</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>16-09-2026</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>245069554267</t>
+          <t>501479897727</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04-01-2006</t>
+          <t>21-03-2007</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 83194 15747</t>
+          <t>+91 94336 92403</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>07535316090</t>
+          <t>09878639784</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2815,19 +2815,19 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>998671043906</t>
+          <t>629829293063</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>15.06.2006</t>
+          <t>08.01.2004</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 97152 63012</t>
+          <t>+91 79887 28283</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>07159072859</t>
+          <t>09778991146</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2892,24 +2892,24 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>251698845083</t>
+          <t>425736478617</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>20.04.2005</t>
+          <t>09.11.2008</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+91 73564 78529</t>
+          <t>+91 91513 92470</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>09721024842</t>
+          <t>07382657552</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2979,19 +2979,19 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>154856604716</t>
+          <t>887531088313</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>20-06-2006</t>
+          <t>24-10-2005</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 94899 36430</t>
+          <t>+91 82570 36633</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>09065020441</t>
+          <t>09347751835</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3073,7 +3073,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>462607089405</t>
+          <t>259848613022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3083,17 +3083,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>28-02-2005</t>
+          <t>25-11-2008</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 98064 86257</t>
+          <t>+91 70457 14796</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>07593111778</t>
+          <t>08903112237</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3143,19 +3143,19 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>10-07-2026</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>516885591091</t>
+          <t>731910584159</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15-03-2008</t>
+          <t>01-12-2004</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 82913 95002</t>
+          <t>+91 96625 37972</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>07693838684</t>
+          <t>08413342926</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3237,7 +3237,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>841359740095</t>
+          <t>321237964254</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3247,17 +3247,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>07/01/2005</t>
+          <t>04.11.2004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 88152 14788</t>
+          <t>+91 86600 29367</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>07381340096</t>
+          <t>07320172909</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3307,19 +3307,19 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>933247685212</t>
+          <t>317598378820</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>02.02.2004</t>
+          <t>14-05-2004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 88517 39758</t>
+          <t>+91 80324 31139</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>08861048392</t>
+          <t>07968703674</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3401,7 +3401,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>304909831301</t>
+          <t>542474250240</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2006-04-27</t>
+          <t>2006-09-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 95826 66933</t>
+          <t>+91 96454 95886</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>07644578983</t>
+          <t>09123188148</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>912607900282</t>
+          <t>705099063220</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>06-04-2007</t>
+          <t>12.07.2004</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 97767 97486</t>
+          <t>+91 90236 27934</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>09542668023</t>
+          <t>09649051040</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3553,19 +3553,19 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>173904933297</t>
+          <t>710579867789</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3575,27 +3575,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2005-05-13</t>
+          <t>2008-06-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 97109 95763</t>
+          <t>+91 92157 88300</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>08715393564</t>
+          <t>07863146476</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>270392822401</t>
+          <t>826455001870</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2008-09-01</t>
+          <t>11.08.2004</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 85287 49046</t>
+          <t>+91 83079 56618</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>08492643443</t>
+          <t>08332949804</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>218185621377</t>
+          <t>702747200588</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3757,17 +3757,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22/11/2005</t>
+          <t>01/10/2007</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 85939 57463</t>
+          <t>+91 89899 75597</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>07995819418</t>
+          <t>08369692738</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3817,19 +3817,19 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>02.08.2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>207560722574</t>
+          <t>589621163466</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3839,27 +3839,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2006-08-04</t>
+          <t>04/03/2008</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 87419 60890</t>
+          <t>+91 76497 42552</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>07863927100</t>
+          <t>09711686820</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>06.06.2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>909183139200</t>
+          <t>763517596237</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>05/01/2006</t>
+          <t>11.12.2007</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 78410 88439</t>
+          <t>+91 90600 17744</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>09852473129</t>
+          <t>09050872413</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3993,7 +3993,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>314140549044</t>
+          <t>593662416891</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22/08/2005</t>
+          <t>2008-09-21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 93466 39775</t>
+          <t>+91 90135 76886</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>09169582727</t>
+          <t>09993148931</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>905202916582</t>
+          <t>427202193975</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,27 +4085,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2008-05-07</t>
+          <t>15-02-2008</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 72498 71166</t>
+          <t>+91 71829 98935</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>07043045725</t>
+          <t>08718793209</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4145,19 +4145,19 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>04.06.2026</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>909196384546</t>
+          <t>624801605623</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2006-01-13</t>
+          <t>23/05/2007</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 87184 62433</t>
+          <t>+91 72236 33783</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>08733369708</t>
+          <t>08695809582</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4227,19 +4227,19 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>19-09-2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>158892941760</t>
+          <t>360139813091</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4249,27 +4249,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2008-04-11</t>
+          <t>16.12.2005</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+91 75194 56474</t>
+          <t>+91 70970 78142</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>09364108950</t>
+          <t>08495893718</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>12.07.2026</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>607897215872</t>
+          <t>380754036167</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,27 +4331,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10.09.2006</t>
+          <t>15/02/2008</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+91 84577 93417</t>
+          <t>+91 98575 73768</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>07343101188</t>
+          <t>08822907011</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>712121818950</t>
+          <t>468929095594</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4413,27 +4413,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2006-08-16</t>
+          <t>13/03/2006</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+91 76131 58711</t>
+          <t>+91 92160 93089</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>07783817080</t>
+          <t>08795125034</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4468,24 +4468,24 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>17/08/2026</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>908394142277</t>
+          <t>332571275900</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2004-03-22</t>
+          <t>09-04-2007</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+91 82492 88415</t>
+          <t>+91 96166 31612</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>09049573930</t>
+          <t>09169807003</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4550,24 +4550,24 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>01/08/2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>791381095636</t>
+          <t>748595455464</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4577,17 +4577,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22-11-2004</t>
+          <t>2005-04-13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+91 97554 89342</t>
+          <t>+91 97825 30902</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>07928858449</t>
+          <t>09765799675</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4632,24 +4632,24 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>564854463755</t>
+          <t>185716635903</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4664,22 +4664,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>05.09.2007</t>
+          <t>23.08.2004</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+91 98100 41520</t>
+          <t>+91 80964 73455</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>09015225265</t>
+          <t>08005351486</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4714,24 +4714,24 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>27.06.2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>197675229536</t>
+          <t>566878956442</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4741,17 +4741,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2004-09-27</t>
+          <t>12-10-2008</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+91 74882 27636</t>
+          <t>+91 71345 95257</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>07020219591</t>
+          <t>09697759124</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>23/08/2026</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>422973620566</t>
+          <t>448323573133</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>14-03-2006</t>
+          <t>2004-09-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+91 99063 95823</t>
+          <t>+91 96242 75973</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>08754262727</t>
+          <t>09845942505</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4878,24 +4878,24 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>417014646747</t>
+          <t>131865298666</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4905,27 +4905,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2007-09-09</t>
+          <t>09/04/2008</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+91 86424 82680</t>
+          <t>+91 80364 29437</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09261336891</t>
+          <t>09147785556</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4965,19 +4965,19 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>01-06-2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>615163798232</t>
+          <t>278360579010</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2007-07-22</t>
+          <t>13-09-2006</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+91 92850 27641</t>
+          <t>+91 92752 45461</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>09529402452</t>
+          <t>07068349946</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5042,24 +5042,24 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>06-09-2026</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>367546404244</t>
+          <t>250440299756</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>05.03.2004</t>
+          <t>2006-09-20</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>+91 78748 99129</t>
+          <t>+91 84553 97711</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>09068150624</t>
+          <t>08118976002</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5124,24 +5124,24 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>26-07-2026</t>
+          <t>27-06-2026</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>788644996327</t>
+          <t>352090035966</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5156,22 +5156,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>18.07.2006</t>
+          <t>15/08/2006</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>+91 91525 37323</t>
+          <t>+91 88718 97741</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>07860134358</t>
+          <t>07005272203</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5206,24 +5206,24 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>184302272274</t>
+          <t>541066433650</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2008-01-13</t>
+          <t>19/01/2004</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>+91 97412 14451</t>
+          <t>+91 74220 92073</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>07516835100</t>
+          <t>09400468709</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>13-09-2026</t>
+          <t>30-07-2026</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>786373350822</t>
+          <t>637752567036</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>12/04/2006</t>
+          <t>19-09-2007</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>+91 97776 67338</t>
+          <t>+91 96004 77980</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09467324934</t>
+          <t>09500933269</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5375,19 +5375,19 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>29/09/2026</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>711020403133</t>
+          <t>649027801325</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5397,27 +5397,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2008-01-14</t>
+          <t>14/06/2008</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>+91 92562 74557</t>
+          <t>+91 76502 40660</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>07340563178</t>
+          <t>09413088872</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>09/07/2026</t>
+          <t>22.09.2026</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5469,7 +5469,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>462371002625</t>
+          <t>653194548332</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5479,27 +5479,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>24-01-2004</t>
+          <t>18-05-2005</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>+91 95921 89379</t>
+          <t>+91 82828 80306</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>08435644196</t>
+          <t>08122342510</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>14/07/2026</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>811462358346</t>
+          <t>292893112872</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01.10.2005</t>
+          <t>2008-04-28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>+91 74661 72396</t>
+          <t>+91 94754 40292</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>07311240558</t>
+          <t>07817151107</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5621,19 +5621,19 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>595544477878</t>
+          <t>423237550993</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5648,22 +5648,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04.03.2005</t>
+          <t>2008-02-05</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>+91 79648 54116</t>
+          <t>+91 72591 57840</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>08873086258</t>
+          <t>07425026303</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>372693176556</t>
+          <t>483478906200</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5725,27 +5725,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>15-05-2004</t>
+          <t>2004-11-04</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>+91 76976 92903</t>
+          <t>+91 71987 94173</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>08345324306</t>
+          <t>09728178974</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>15/07/2026</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>410570826663</t>
+          <t>831118321932</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5807,17 +5807,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>16-07-2008</t>
+          <t>12-08-2007</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>+91 79314 44584</t>
+          <t>+91 85350 53907</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>07809642225</t>
+          <t>08291271595</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5867,19 +5867,19 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>688907959686</t>
+          <t>912574910687</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5889,27 +5889,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2004-04-11</t>
+          <t>08/02/2004</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>+91 97506 18045</t>
+          <t>+91 77692 50422</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>09311242529</t>
+          <t>08389407016</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5961,7 +5961,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>489574942730</t>
+          <t>813103300522</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>10.07.2008</t>
+          <t>2004-07-25</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>+91 93345 47802</t>
+          <t>+91 96051 20385</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>09250449560</t>
+          <t>09042321651</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>20.09.2026</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>259665633768</t>
+          <t>152773497555</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22-04-2008</t>
+          <t>18/01/2004</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>+91 96828 22515</t>
+          <t>+91 86539 50304</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>09226794717</t>
+          <t>08992842350</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6108,24 +6108,24 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>466017347670</t>
+          <t>228192758095</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6135,27 +6135,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>23/09/2005</t>
+          <t>10-08-2005</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>+91 80183 21473</t>
+          <t>+91 92149 24983</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>08924270785</t>
+          <t>07592300054</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6190,24 +6190,24 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>08/07/2026</t>
+          <t>07-06-2026</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>223018514600</t>
+          <t>179506314237</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6217,27 +6217,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22.04.2004</t>
+          <t>22-08-2007</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>+91 84017 25403</t>
+          <t>+91 83749 50320</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>08528173370</t>
+          <t>08231925637</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>02/08/2026</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">

--- a/samples/sample_1_excess_intake.xlsx
+++ b/samples/sample_1_excess_intake.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P74"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>873923542950</t>
+          <t>452661932490</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13/06/2005</t>
+          <t>14/06/2004</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+91 96583 76369</t>
+          <t>+91 75057 69614</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>07899355976</t>
+          <t>07194975212</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>28-09-2026</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>312914950317</t>
+          <t>203671869026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -610,22 +610,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13/08/2007</t>
+          <t>08.01.2007</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+91 94871 12620</t>
+          <t>+91 78794 95899</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>08145757506</t>
+          <t>08711801006</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -660,12 +660,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -677,7 +677,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>780264275923</t>
+          <t>686674257897</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -687,17 +687,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>27/02/2006</t>
+          <t>2004-10-09</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -707,7 +707,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+91 81089 40725</t>
+          <t>+91 80688 43446</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>09969113350</t>
+          <t>09502069455</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,24 +742,24 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>09.08.2026</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>637031822213</t>
+          <t>123828472556</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -774,22 +774,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2008-02-18</t>
+          <t>25/05/2007</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+91 93885 86594</t>
+          <t>+91 97975 49780</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>08911848521</t>
+          <t>07270248074</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -809,12 +809,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -829,19 +829,19 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>30-09-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>684534811895</t>
+          <t>312495548925</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25-03-2005</t>
+          <t>27-06-2007</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+91 86502 91787</t>
+          <t>+91 75190 44244</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>07848892378</t>
+          <t>08888693853</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>16-08-2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>700012492256</t>
+          <t>842813883772</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>03-11-2008</t>
+          <t>2007-08-21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+91 79689 54988</t>
+          <t>+91 81116 78785</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>07943996495</t>
+          <t>09422539408</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -988,12 +988,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>12.09.2026</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>559095358077</t>
+          <t>227662247601</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>27.05.2007</t>
+          <t>20-02-2006</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+91 91730 13359</t>
+          <t>+91 72662 43552</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>07866759867</t>
+          <t>08546264509</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1075,19 +1075,19 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>30/08/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>579185746457</t>
+          <t>771633537656</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1097,27 +1097,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2007-06-27</t>
+          <t>24-03-2008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+91 84616 63366</t>
+          <t>+91 81262 88640</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>08795131191</t>
+          <t>09430461176</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1137,12 +1137,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1152,24 +1152,24 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>937976137248</t>
+          <t>596014236271</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2004-01-03</t>
+          <t>11/01/2005</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+91 93205 29468</t>
+          <t>+91 92577 77585</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>09596064016</t>
+          <t>08110517152</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>916562398890</t>
+          <t>286403367577</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>22-07-2006</t>
+          <t>2007-10-05</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+91 70096 94652</t>
+          <t>+91 89815 50903</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>09143272812</t>
+          <t>08531509480</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1321,19 +1321,19 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>13/08/2026</t>
+          <t>04/07/2026</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>190713794933</t>
+          <t>198428144388</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1343,27 +1343,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2005-06-14</t>
+          <t>2004-12-04</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+91 95893 30253</t>
+          <t>+91 79093 46344</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>08636759492</t>
+          <t>07821293682</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1398,24 +1398,24 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>720499500655</t>
+          <t>809209498752</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>24-09-2007</t>
+          <t>2004-05-22</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+91 71668 35887</t>
+          <t>+91 73184 54510</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>07210138901</t>
+          <t>07414900223</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>125368456450</t>
+          <t>245075794394</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>20.12.2004</t>
+          <t>17/06/2005</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+91 94542 88669</t>
+          <t>+91 73162 19007</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>09158575829</t>
+          <t>09019418047</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1585,19 +1585,19 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>317528375691</t>
+          <t>874636722004</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24-07-2008</t>
+          <t>15-08-2006</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+91 99781 20469</t>
+          <t>+91 75858 73542</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>08378813437</t>
+          <t>08258042768</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1667,19 +1667,19 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>11/07/2026</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>668313629943</t>
+          <t>919975714918</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1689,17 +1689,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>24-07-2008</t>
+          <t>21/07/2005</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+91 97712 24325</t>
+          <t>+91 71111 75783</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>07840701489</t>
+          <t>07048904334</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>18.07.2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>855566208562</t>
+          <t>464489369321</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13-05-2005</t>
+          <t>06/10/2004</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+91 76418 74217</t>
+          <t>+91 85891 15648</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>09271753193</t>
+          <t>08162588096</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>23.06.2026</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>563808144683</t>
+          <t>628355491356</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28-12-2007</t>
+          <t>20-04-2004</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+91 96352 76091</t>
+          <t>+91 73416 71925</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>08153654077</t>
+          <t>09395862318</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1893,12 +1893,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1908,24 +1908,24 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>05.07.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>922506488115</t>
+          <t>124595579071</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1935,27 +1935,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2006-04-08</t>
+          <t>2004-01-20</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+91 87211 35609</t>
+          <t>+91 80881 78457</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>08580292163</t>
+          <t>07251193581</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1990,24 +1990,24 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>24.06.2026</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>963482292665</t>
+          <t>641951804619</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2017,27 +2017,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>06/11/2004</t>
+          <t>09/02/2007</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+91 92447 44686</t>
+          <t>+91 84213 71491</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>07373854687</t>
+          <t>09225749878</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2077,19 +2077,19 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>30-08-2026</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>821471690399</t>
+          <t>409584723777</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>05-02-2008</t>
+          <t>2008-04-08</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+91 98149 27997</t>
+          <t>+91 86791 99279</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09807371788</t>
+          <t>09289048830</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>04-07-2026</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>494037713474</t>
+          <t>909066576754</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2186,22 +2186,22 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08/06/2008</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+91 93638 89892</t>
+          <t>+91 92696 59206</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>08494848912</t>
+          <t>09542619072</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2236,24 +2236,24 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>172079013329</t>
+          <t>328897862405</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,27 +2263,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2007-03-14</t>
+          <t>2008-04-17</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+91 75789 54165</t>
+          <t>+91 75158 82607</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>07854388522</t>
+          <t>07130695457</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2318,24 +2318,24 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>908494315009</t>
+          <t>491754713250</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2345,17 +2345,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>21/09/2005</t>
+          <t>11/03/2008</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+91 72718 28021</t>
+          <t>+91 83276 80225</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>07569745084</t>
+          <t>08158260504</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2417,7 +2417,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>166316080098</t>
+          <t>343241508351</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>05-03-2005</t>
+          <t>20-04-2007</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+91 88951 99987</t>
+          <t>+91 70682 81901</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>08597911366</t>
+          <t>09642274202</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2487,19 +2487,19 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>15-07-2026</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>404246197950</t>
+          <t>181124958167</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2509,27 +2509,27 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>16-11-2006</t>
+          <t>03-06-2007</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+91 87252 61204</t>
+          <t>+91 87353 30446</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>07578904703</t>
+          <t>08794882773</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2564,24 +2564,24 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>23/07/2026</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>511753973988</t>
+          <t>377769030136</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02-07-2006</t>
+          <t>12.12.2007</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+91 70905 91452</t>
+          <t>+91 87742 91299</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>07615153189</t>
+          <t>09301915580</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2646,24 +2646,24 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>720302914508</t>
+          <t>937131336241</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2673,27 +2673,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>25-03-2008</t>
+          <t>2008-12-11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+91 89701 95973</t>
+          <t>+91 84096 36967</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>08583639297</t>
+          <t>08851784025</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>16-09-2026</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2745,7 +2745,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>501479897727</t>
+          <t>245069554267</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>21-03-2007</t>
+          <t>04-01-2006</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2770,12 +2770,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+91 94336 92403</t>
+          <t>+91 83194 15747</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>09878639784</t>
+          <t>07535316090</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2815,19 +2815,19 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>629829293063</t>
+          <t>998671043906</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>08.01.2004</t>
+          <t>15.06.2006</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+91 79887 28283</t>
+          <t>+91 97152 63012</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>09778991146</t>
+          <t>07159072859</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2892,24 +2892,24 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>425736478617</t>
+          <t>251698845083</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2919,27 +2919,27 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>09.11.2008</t>
+          <t>20.04.2005</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+91 91513 92470</t>
+          <t>+91 73564 78529</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>07382657552</t>
+          <t>09721024842</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2979,19 +2979,19 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>29.07.2026</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>887531088313</t>
+          <t>154856604716</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>24-10-2005</t>
+          <t>20-06-2006</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+91 82570 36633</t>
+          <t>+91 94899 36430</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>09347751835</t>
+          <t>09065020441</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3073,7 +3073,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>259848613022</t>
+          <t>462607089405</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3083,17 +3083,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>25-11-2008</t>
+          <t>28-02-2005</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+91 70457 14796</t>
+          <t>+91 98064 86257</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>08903112237</t>
+          <t>07593111778</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3123,12 +3123,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3143,19 +3143,19 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>10-07-2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>731910584159</t>
+          <t>516885591091</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>01-12-2004</t>
+          <t>15-03-2008</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+91 96625 37972</t>
+          <t>+91 82913 95002</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>08413342926</t>
+          <t>07693838684</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3237,7 +3237,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>321237964254</t>
+          <t>841359740095</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3247,17 +3247,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>04.11.2004</t>
+          <t>07/01/2005</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+91 86600 29367</t>
+          <t>+91 88152 14788</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>07320172909</t>
+          <t>07381340096</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3307,19 +3307,19 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>317598378820</t>
+          <t>933247685212</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3334,12 +3334,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>14-05-2004</t>
+          <t>02.02.2004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+91 80324 31139</t>
+          <t>+91 88517 39758</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>07968703674</t>
+          <t>08861048392</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3369,12 +3369,12 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3401,7 +3401,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>542474250240</t>
+          <t>304909831301</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3411,27 +3411,27 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2006-09-09</t>
+          <t>2006-04-27</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+91 96454 95886</t>
+          <t>+91 95826 66933</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>09123188148</t>
+          <t>07644578983</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>705099063220</t>
+          <t>912607900282</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>12.07.2004</t>
+          <t>06-04-2007</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+91 90236 27934</t>
+          <t>+91 97767 97486</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>09649051040</t>
+          <t>09542668023</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3553,19 +3553,19 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>710579867789</t>
+          <t>173904933297</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3575,27 +3575,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2008-06-20</t>
+          <t>2005-05-13</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+91 92157 88300</t>
+          <t>+91 97109 95763</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>07863146476</t>
+          <t>08715393564</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3647,7 +3647,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>826455001870</t>
+          <t>270392822401</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3657,17 +3657,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>11.08.2004</t>
+          <t>2008-09-01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+91 83079 56618</t>
+          <t>+91 85287 49046</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>08332949804</t>
+          <t>08492643443</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>25.08.2026</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -3747,7 +3747,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>702747200588</t>
+          <t>218185621377</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3757,17 +3757,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>01/10/2007</t>
+          <t>22/11/2005</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+91 89899 75597</t>
+          <t>+91 85939 57463</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>08369692738</t>
+          <t>07995819418</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3817,19 +3817,19 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>02.08.2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>589621163466</t>
+          <t>207560722574</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3839,27 +3839,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>04/03/2008</t>
+          <t>2006-08-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+91 76497 42552</t>
+          <t>+91 87419 60890</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>09711686820</t>
+          <t>07863927100</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3899,7 +3899,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>06.06.2026</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>763517596237</t>
+          <t>909183139200</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.12.2007</t>
+          <t>05/01/2006</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+91 90600 17744</t>
+          <t>+91 78410 88439</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>09050872413</t>
+          <t>09852473129</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3993,7 +3993,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>593662416891</t>
+          <t>314140549044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2008-09-21</t>
+          <t>22/08/2005</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+91 90135 76886</t>
+          <t>+91 93466 39775</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>09993148931</t>
+          <t>09169582727</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>13/07/2026</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4075,7 +4075,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>427202193975</t>
+          <t>905202916582</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4085,27 +4085,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>15-02-2008</t>
+          <t>2008-05-07</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+91 71829 98935</t>
+          <t>+91 72498 71166</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08718793209</t>
+          <t>07043045725</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4145,19 +4145,19 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>04.06.2026</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>624801605623</t>
+          <t>909196384546</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>23/05/2007</t>
+          <t>2006-01-13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+91 72236 33783</t>
+          <t>+91 87184 62433</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>08695809582</t>
+          <t>08733369708</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4227,19 +4227,19 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>19-09-2026</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>360139813091</t>
+          <t>158892941760</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4249,27 +4249,27 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>16.12.2005</t>
+          <t>2008-04-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+91 70970 78142</t>
+          <t>+91 75194 56474</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>08495893718</t>
+          <t>09364108950</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>12.07.2026</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>380754036167</t>
+          <t>607897215872</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4331,27 +4331,27 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>15/02/2008</t>
+          <t>10.09.2006</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+91 98575 73768</t>
+          <t>+91 84577 93417</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>08822907011</t>
+          <t>07343101188</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>468929095594</t>
+          <t>712121818950</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4413,27 +4413,27 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13/03/2006</t>
+          <t>2006-08-16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+91 92160 93089</t>
+          <t>+91 76131 58711</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>08795125034</t>
+          <t>07783817080</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4468,24 +4468,24 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>17/08/2026</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>332571275900</t>
+          <t>908394142277</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4500,22 +4500,22 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>09-04-2007</t>
+          <t>2004-03-22</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+91 96166 31612</t>
+          <t>+91 82492 88415</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>09169807003</t>
+          <t>09049573930</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4550,24 +4550,24 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>01/08/2026</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>748595455464</t>
+          <t>791381095636</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4577,17 +4577,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2005-04-13</t>
+          <t>22-11-2004</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>+91 97825 30902</t>
+          <t>+91 97554 89342</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>09765799675</t>
+          <t>07928858449</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4632,24 +4632,24 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>26-09-2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>185716635903</t>
+          <t>564854463755</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4664,22 +4664,22 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>23.08.2004</t>
+          <t>05.09.2007</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>+91 80964 73455</t>
+          <t>+91 98100 41520</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>08005351486</t>
+          <t>09015225265</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4714,24 +4714,24 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>27.06.2026</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>566878956442</t>
+          <t>197675229536</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4741,17 +4741,17 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>12-10-2008</t>
+          <t>2004-09-27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>+91 71345 95257</t>
+          <t>+91 74882 27636</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>09697759124</t>
+          <t>07020219591</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4781,12 +4781,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>23/08/2026</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4813,7 +4813,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>448323573133</t>
+          <t>422973620566</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4823,27 +4823,27 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>14-03-2006</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+91 96242 75973</t>
+          <t>+91 99063 95823</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>09845942505</t>
+          <t>08754262727</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4878,24 +4878,24 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>131865298666</t>
+          <t>417014646747</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4905,27 +4905,27 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>09/04/2008</t>
+          <t>2007-09-09</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>+91 80364 29437</t>
+          <t>+91 86424 82680</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4935,7 +4935,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>09147785556</t>
+          <t>09261336891</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4965,19 +4965,19 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>01-06-2026</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>278360579010</t>
+          <t>615163798232</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>13-09-2006</t>
+          <t>2007-07-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+91 92752 45461</t>
+          <t>+91 92850 27641</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -5017,7 +5017,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>07068349946</t>
+          <t>09529402452</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5042,24 +5042,24 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>06-09-2026</t>
+          <t>18.09.2026</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>250440299756</t>
+          <t>367546404244</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2006-09-20</t>
+          <t>05.03.2004</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>+91 84553 97711</t>
+          <t>+91 78748 99129</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>08118976002</t>
+          <t>09068150624</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5124,24 +5124,24 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>27-06-2026</t>
+          <t>26-07-2026</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>352090035966</t>
+          <t>788644996327</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5156,22 +5156,22 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>15/08/2006</t>
+          <t>18.07.2006</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>+91 88718 97741</t>
+          <t>+91 91525 37323</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>07005272203</t>
+          <t>07860134358</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5206,24 +5206,24 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>541066433650</t>
+          <t>184302272274</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19/01/2004</t>
+          <t>2008-01-13</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>+91 74220 92073</t>
+          <t>+91 97412 14451</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>09400468709</t>
+          <t>07516835100</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>30-07-2026</t>
+          <t>13-09-2026</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>637752567036</t>
+          <t>786373350822</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>19-09-2007</t>
+          <t>12/04/2006</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>EWS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>+91 96004 77980</t>
+          <t>+91 97776 67338</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>09500933269</t>
+          <t>09467324934</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5375,19 +5375,19 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>29/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>649027801325</t>
+          <t>711020403133</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5397,27 +5397,27 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>14/06/2008</t>
+          <t>2008-01-14</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>+91 76502 40660</t>
+          <t>+91 92562 74557</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>09413088872</t>
+          <t>07340563178</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>09/07/2026</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -5469,7 +5469,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>653194548332</t>
+          <t>462371002625</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5479,27 +5479,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>female</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>18-05-2005</t>
+          <t>24-01-2004</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OBC-NCL</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>+91 82828 80306</t>
+          <t>+91 95921 89379</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>08122342510</t>
+          <t>08435644196</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5534,12 +5534,12 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>14/07/2026</t>
+          <t>26-09-2026</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -5551,7 +5551,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>292893112872</t>
+          <t>811462358346</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5561,27 +5561,27 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2008-04-28</t>
+          <t>01.10.2005</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>+91 94754 40292</t>
+          <t>+91 74661 72396</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>07817151107</t>
+          <t>07311240558</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5621,19 +5621,19 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>13.08.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>423237550993</t>
+          <t>595544477878</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5648,22 +5648,22 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2008-02-05</t>
+          <t>04.03.2005</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>+91 72591 57840</t>
+          <t>+91 79648 54116</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>07425026303</t>
+          <t>08873086258</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5698,24 +5698,24 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>483478906200</t>
+          <t>372693176556</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5725,27 +5725,27 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2004-11-04</t>
+          <t>15-05-2004</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>obc</t>
+          <t>OBC-NCL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>+91 71987 94173</t>
+          <t>+91 76976 92903</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>09728178974</t>
+          <t>08345324306</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2026-2027</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5780,12 +5780,12 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>15/07/2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -5797,7 +5797,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>831118321932</t>
+          <t>410570826663</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5807,17 +5807,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>12-08-2007</t>
+          <t>16-07-2008</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>EWS</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>+91 85350 53907</t>
+          <t>+91 79314 44584</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>08291271595</t>
+          <t>07809642225</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5867,19 +5867,19 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>22-07-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>912574910687</t>
+          <t>688907959686</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5889,27 +5889,27 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>M</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>08/02/2004</t>
+          <t>2004-04-11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>obc</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>indian</t>
+          <t>Indian</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>+91 77692 50422</t>
+          <t>+91 97506 18045</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>08389407016</t>
+          <t>09311242529</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>Regular</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>13/07/2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5961,7 +5961,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>813103300522</t>
+          <t>489574942730</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2004-07-25</t>
+          <t>10.07.2008</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5986,12 +5986,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Indian</t>
+          <t>INDIAN</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>+91 96051 20385</t>
+          <t>+91 93345 47802</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>09042321651</t>
+          <t>09250449560</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>20.09.2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -6043,7 +6043,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>152773497555</t>
+          <t>259665633768</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>18/01/2004</t>
+          <t>22-04-2008</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>+91 86539 50304</t>
+          <t>+91 96828 22515</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>08992842350</t>
+          <t>09226794717</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6108,24 +6108,24 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Regular</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>04/07/2026</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Admitted</t>
+          <t>admitted</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>228192758095</t>
+          <t>466017347670</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6135,27 +6135,27 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>10-08-2005</t>
+          <t>23/09/2005</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>INDIAN</t>
+          <t>indian</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>+91 92149 24983</t>
+          <t>+91 80183 21473</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>07592300054</t>
+          <t>08924270785</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-2027</t>
+          <t>2026-27</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6190,24 +6190,24 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>regular</t>
+          <t>REGULAR</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>07-06-2026</t>
+          <t>08/07/2026</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>admitted</t>
+          <t>Admitted</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>179506314237</t>
+          <t>223018514600</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6217,96 +6217,1162 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22.04.2004</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>+91 84017 25403</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>student69@example.invalid</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>08528173370</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>774856838093</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Imran Qureshi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04.01.2004</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>+91 74637 71569</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>student70@example.invalid</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>08631063987</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>634592634699</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Divya Pillai</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
           <t>female</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>22-08-2007</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>11-01-2004</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>obc</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>+91 74713 17850</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>student71@example.invalid</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>07741725082</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>427691334219</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sandeep Yadav</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2006-05-02</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>+91 99264 60220</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>student72@example.invalid</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>09399812805</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>07.06.2026</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>957792614967</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Meera Joshi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2008-04-22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>+91 91292 95218</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>student73@example.invalid</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>08183630465</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>431668627350</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tarun Bose</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19.07.2004</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>obc</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>+91 93511 61283</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>student74@example.invalid</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>08021590930</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>816562753200</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rahul Sharma</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>03/12/2005</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>+91 71454 17029</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>student75@example.invalid</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>08846666988</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>425437956182</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Aisha Khan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>15.10.2008</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>+91 82652 23076</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>student76@example.invalid</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>08597068460</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>445965346770</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Vikram Patel</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2004-02-23</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>indian</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>+91 83749 50320</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>student69@example.invalid</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>08231925637</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>CSE</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>+91 76038 71851</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>student77@example.invalid</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>09117348339</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>2026-2027</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>660348529498</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sneha Iyer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>25/01/2007</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>+91 80199 99446</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>student78@example.invalid</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>07474038401</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>573167559469</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Arjun Nair</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2005-09-07</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>+91 84148 81191</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>student79@example.invalid</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>07099651897</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>527322515085</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Priya Menon</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2007-09-26</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>+91 74844 35323</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>student80@example.invalid</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>08108405473</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>212020554871</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Rohit Verma</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2004-07-06</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>+91 85169 26461</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>student81@example.invalid</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>08200356137</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>regular</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>02/08/2026</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>854461920326</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Fatima Shaikh</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2005-01-22</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>+91 74312 20961</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>student82@example.invalid</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>08551163422</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
         <is>
           <t>Admitted</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>TOTAL = 70</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TOTAL = 83</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/sample_1_excess_intake.xlsx
+++ b/samples/sample_1_excess_intake.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Electrical Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5303,2076 +5303,26 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>786373350822</t>
-        </is>
-      </c>
+      <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Meera Joshi</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>12/04/2006</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>+91 97776 67338</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>student58@example.invalid</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>09467324934</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>07/09/2026</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>711020403133</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tarun Bose</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>2008-01-14</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>+91 92562 74557</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>student59@example.invalid</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>07340563178</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>09/07/2026</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>462371002625</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Rahul Sharma</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>24-01-2004</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>+91 95921 89379</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>student60@example.invalid</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>08435644196</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>26-09-2026</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>811462358346</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Aisha Khan</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>01.10.2005</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>+91 74661 72396</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>student61@example.invalid</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>07311240558</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>10.07.2026</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>595544477878</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Vikram Patel</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>04.03.2005</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>+91 79648 54116</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>student62@example.invalid</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>08873086258</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>372693176556</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Sneha Iyer</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>15-05-2004</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>+91 76976 92903</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>student63@example.invalid</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>08345324306</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>15.07.2026</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>410570826663</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Arjun Nair</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>16-07-2008</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>+91 79314 44584</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>student64@example.invalid</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>07809642225</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>688907959686</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Priya Menon</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2004-04-11</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>+91 97506 18045</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>student65@example.invalid</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>09311242529</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>489574942730</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Rohit Verma</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>10.07.2008</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>+91 93345 47802</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>student66@example.invalid</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>09250449560</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>259665633768</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Fatima Shaikh</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>22-04-2008</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>+91 96828 22515</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>student67@example.invalid</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>09226794717</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>466017347670</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Karthik Reddy</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>23/09/2005</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>+91 80183 21473</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>student68@example.invalid</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>08924270785</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>223018514600</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Neha Gupta</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>22.04.2004</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>+91 84017 25403</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>student69@example.invalid</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>08528173370</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>774856838093</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Imran Qureshi</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>04.01.2004</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>+91 74637 71569</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>student70@example.invalid</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>08631063987</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>634592634699</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Divya Pillai</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>11-01-2004</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>+91 74713 17850</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>student71@example.invalid</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>07741725082</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>427691334219</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Sandeep Yadav</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2006-05-02</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>+91 99264 60220</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>student72@example.invalid</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>09399812805</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>07.06.2026</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>957792614967</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Meera Joshi</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2008-04-22</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>+91 91292 95218</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>student73@example.invalid</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>08183630465</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>30.07.2026</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>431668627350</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Tarun Bose</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>19.07.2004</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>+91 93511 61283</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>student74@example.invalid</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>08021590930</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>816562753200</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Rahul Sharma</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>03/12/2005</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>+91 71454 17029</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>student75@example.invalid</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>08846666988</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>425437956182</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Aisha Khan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>15.10.2008</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>+91 82652 23076</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>student76@example.invalid</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>08597068460</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>445965346770</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Vikram Patel</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2004-02-23</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>+91 76038 71851</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>student77@example.invalid</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>09117348339</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>660348529498</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Sneha Iyer</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>25/01/2007</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>+91 80199 99446</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>student78@example.invalid</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>07474038401</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>573167559469</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Arjun Nair</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2005-09-07</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>+91 84148 81191</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>student79@example.invalid</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>07099651897</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>527322515085</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Priya Menon</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2007-09-26</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>+91 74844 35323</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>student80@example.invalid</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>08108405473</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>212020554871</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Rohit Verma</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2004-07-06</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>+91 85169 26461</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>student81@example.invalid</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>08200356137</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>854461920326</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Fatima Shaikh</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2005-01-22</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>+91 74312 20961</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>student82@example.invalid</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>08551163422</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Electrical Engineering</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>04.08.2026</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TOTAL = 83</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+          <t>TOTAL = 58</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/sample_1_excess_intake.xlsx
+++ b/samples/sample_1_excess_intake.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Civil Engineering</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5303,26 +5303,2076 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>786373350822</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TOTAL = 58</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+          <t>Meera Joshi</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>12/04/2006</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>+91 97776 67338</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>student58@example.invalid</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>09467324934</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>711020403133</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Tarun Bose</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2008-01-14</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>+91 92562 74557</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>student59@example.invalid</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>07340563178</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>09/07/2026</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>462371002625</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Rahul Sharma</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>24-01-2004</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>obc</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>+91 95921 89379</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>student60@example.invalid</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>08435644196</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>811462358346</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Aisha Khan</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>01.10.2005</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>+91 74661 72396</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>student61@example.invalid</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>07311240558</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>10.07.2026</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>595544477878</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Vikram Patel</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>04.03.2005</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>+91 79648 54116</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>student62@example.invalid</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>08873086258</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>372693176556</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Sneha Iyer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>15-05-2004</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>+91 76976 92903</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>student63@example.invalid</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>08345324306</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>15.07.2026</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>410570826663</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Arjun Nair</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>16-07-2008</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>+91 79314 44584</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>student64@example.invalid</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>07809642225</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>688907959686</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Priya Menon</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2004-04-11</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>obc</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>+91 97506 18045</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>student65@example.invalid</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>09311242529</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>489574942730</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Rohit Verma</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>10.07.2008</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>+91 93345 47802</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>student66@example.invalid</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>09250449560</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>259665633768</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Fatima Shaikh</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>22-04-2008</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>+91 96828 22515</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>student67@example.invalid</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>09226794717</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>466017347670</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Karthik Reddy</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>23/09/2005</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>+91 80183 21473</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>student68@example.invalid</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>08924270785</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>223018514600</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22.04.2004</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>+91 84017 25403</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>student69@example.invalid</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>08528173370</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>774856838093</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Imran Qureshi</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>04.01.2004</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>+91 74637 71569</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>student70@example.invalid</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>08631063987</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>634592634699</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Divya Pillai</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>11-01-2004</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>obc</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>+91 74713 17850</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>student71@example.invalid</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>07741725082</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>09/09/2026</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>427691334219</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Sandeep Yadav</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2006-05-02</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>+91 99264 60220</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>student72@example.invalid</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>09399812805</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>07.06.2026</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>957792614967</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Meera Joshi</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2008-04-22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>+91 91292 95218</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>student73@example.invalid</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>08183630465</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>30.07.2026</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>431668627350</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Tarun Bose</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>19.07.2004</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>obc</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>+91 93511 61283</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>student74@example.invalid</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>08021590930</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>26-06-2026</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>816562753200</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Rahul Sharma</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>03/12/2005</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>+91 71454 17029</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>student75@example.invalid</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>08846666988</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>425437956182</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Aisha Khan</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>15.10.2008</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>+91 82652 23076</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>student76@example.invalid</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>08597068460</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>445965346770</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Vikram Patel</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2004-02-23</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>EWS</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>+91 76038 71851</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>student77@example.invalid</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>09117348339</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>660348529498</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Sneha Iyer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>25/01/2007</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>+91 80199 99446</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>student78@example.invalid</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>07474038401</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>01-07-2026</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>573167559469</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Arjun Nair</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2005-09-07</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>+91 84148 81191</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>student79@example.invalid</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>07099651897</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>527322515085</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Priya Menon</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2007-09-26</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>GEN</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>+91 74844 35323</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>student80@example.invalid</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>08108405473</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>REGULAR</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>23.07.2026</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>212020554871</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Rohit Verma</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2004-07-06</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>indian</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>+91 85169 26461</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>student81@example.invalid</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>08200356137</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>2026-2027</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>854461920326</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Fatima Shaikh</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2005-01-22</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OBC-NCL</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>INDIAN</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>+91 74312 20961</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>student82@example.invalid</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>08551163422</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>B.Tech</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Civil Engineering</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>regular</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>04.08.2026</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>TOTAL = 83</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/sample_1_excess_intake.xlsx
+++ b/samples/sample_1_excess_intake.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P87"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,7 +563,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4945,7 +4945,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5683,7 +5683,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Civil Engineering</t>
+          <t>Electrical Engineering</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5713,1666 +5713,26 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>372693176556</t>
-        </is>
-      </c>
+      <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sneha Iyer</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>15-05-2004</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>+91 76976 92903</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>student63@example.invalid</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>08345324306</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>15.07.2026</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>410570826663</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Arjun Nair</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>16-07-2008</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>+91 79314 44584</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>student64@example.invalid</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>07809642225</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>688907959686</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Priya Menon</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>2004-04-11</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>+91 97506 18045</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>student65@example.invalid</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>09311242529</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>489574942730</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Rohit Verma</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>10.07.2008</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>+91 93345 47802</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>student66@example.invalid</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>09250449560</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>259665633768</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Fatima Shaikh</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>22-04-2008</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>+91 96828 22515</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>student67@example.invalid</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>09226794717</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>466017347670</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Karthik Reddy</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>23/09/2005</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>+91 80183 21473</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>student68@example.invalid</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>08924270785</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>08/07/2026</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>223018514600</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Neha Gupta</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>22.04.2004</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>+91 84017 25403</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>student69@example.invalid</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>08528173370</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>774856838093</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Imran Qureshi</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>04.01.2004</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>+91 74637 71569</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>student70@example.invalid</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>08631063987</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>634592634699</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Divya Pillai</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>11-01-2004</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>+91 74713 17850</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>student71@example.invalid</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>07741725082</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>09/09/2026</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>427691334219</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Sandeep Yadav</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2006-05-02</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>+91 99264 60220</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>student72@example.invalid</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>09399812805</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>07.06.2026</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>957792614967</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Meera Joshi</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2008-04-22</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>+91 91292 95218</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>student73@example.invalid</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>08183630465</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>30.07.2026</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>431668627350</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Tarun Bose</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>19.07.2004</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>obc</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>+91 93511 61283</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>student74@example.invalid</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>08021590930</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>26-06-2026</t>
-        </is>
-      </c>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>816562753200</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Rahul Sharma</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>03/12/2005</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>+91 71454 17029</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>student75@example.invalid</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>08846666988</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>425437956182</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Aisha Khan</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>15.10.2008</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ST</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>+91 82652 23076</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>student76@example.invalid</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>08597068460</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
-      </c>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>445965346770</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Vikram Patel</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2004-02-23</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>EWS</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>+91 76038 71851</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>student77@example.invalid</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>09117348339</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>660348529498</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Sneha Iyer</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>25/01/2007</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>+91 80199 99446</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>student78@example.invalid</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>07474038401</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>01-07-2026</t>
-        </is>
-      </c>
-      <c r="P82" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>573167559469</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Arjun Nair</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2005-09-07</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>+91 84148 81191</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>student79@example.invalid</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>07099651897</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>2026-06-07</t>
-        </is>
-      </c>
-      <c r="P83" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>527322515085</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Priya Menon</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2007-09-26</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>GEN</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Indian</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>+91 74844 35323</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>student80@example.invalid</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>08108405473</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>REGULAR</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>23.07.2026</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>212020554871</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Rohit Verma</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>2004-07-06</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>indian</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>+91 85169 26461</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>student81@example.invalid</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>08200356137</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>2026-2027</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>854461920326</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Fatima Shaikh</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>2005-01-22</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>OBC-NCL</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>INDIAN</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>+91 74312 20961</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>student82@example.invalid</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>08551163422</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>B.Tech</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Civil Engineering</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>2026-27</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>regular</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>04.08.2026</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>Admitted</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>TOTAL = 83</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+          <t>TOTAL = 63</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
